--- a/reports/youtube-analysis-2026-09-11.xlsx
+++ b/reports/youtube-analysis-2026-09-11.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -687,11 +687,11 @@
         <v>37.7</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>21.7</v>
+        <v>30.3</v>
       </c>
       <c r="N5" s="8">
-        <f>IF(F5=0,"",13/F5)</f>
-        <v>0.26</v>
+        <f>IF(F5=0,"",3/F5)</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="6">
@@ -855,11 +855,11 @@
         <v>49.2</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>20.3</v>
+        <v>30.6</v>
       </c>
       <c r="N8" s="8">
-        <f>IF(F8=0,"",23/F8)</f>
-        <v>0.46</v>
+        <f>IF(F8=0,"",9/F8)</f>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9">
@@ -911,11 +911,11 @@
         <v>44</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>23.4</v>
+        <v>30.2</v>
       </c>
       <c r="N9" s="8">
-        <f>IF(F9=0,"",13/F9)</f>
-        <v>0.265306</v>
+        <f>IF(F9=0,"",4/F9)</f>
+        <v>0.081633</v>
       </c>
     </row>
     <row r="10">
@@ -967,11 +967,11 @@
         <v>49.3</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>23.2</v>
+        <v>32</v>
       </c>
       <c r="N10" s="8">
-        <f>IF(F10=0,"",18/F10)</f>
-        <v>0.367347</v>
+        <f>IF(F10=0,"",5/F10)</f>
+        <v>0.102041</v>
       </c>
     </row>
     <row r="11">
@@ -1247,7 +1247,7 @@
         <v>42.7</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="N15" s="8">
         <f>IF(F15=0,"",7/F15)</f>
@@ -1379,14 +1379,14 @@
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>② タイトル実効文字数と登録転換に強い関係があった（n=330）。0-14字 0.242 / 15-19字 0.279 / 20-24字 0.400 / 25-29字 0.637 / 30字以上 0.355。25〜29字を頂点とする逆U字で、全330本のうち112本（34%）が20字未満だった。自然文の min_effective_chars_target は backend が読まないため1本も効いていなかったので、本日 title_constraints.py に機械ゲートとして実装し8chへ適用した。</t>
+          <t>② タイトル実効文字数と登録転換に強い関係があった（n=330）。0-14字 0.104 / 15-19字 0.279 / 20-24字 0.402 / 25-29字 0.646 / 30-34字 0.389 / 35字以上 0.345。25〜29字を頂点とする逆U字で、20字未満は最良帯の 1/2.3〜1/6.2。帯の切り方に依存しないことを4分位でも確認した（Q1 9-21字 0.227 / Q2 0.476 / Q3 27-35字 0.518 / Q4 35-54字 0.352）。20字未満は全330本中66本（20%）。自然文の min_effective_chars_target は backend が読まないため1本も効いていなかったので、本日 title_constraints.py に機械ゲートとして実装し8chへ適用した。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>③ 切り抜き3chは再生の46%（89,707再生）を占めながら登録獲得は10人で、ゆっくり系との登録効率差は依然として大きい。平均タイトル実効長も 16.1〜19.3字で全ch最短。ただし切り抜きのタイトルは発言の引用なので、文字数下限を課すと誤引用を作るリスクがある。本日は適用を見送り、別施策（引用は保ったまま文脈を添える形）として扱う。</t>
+          <t>③ 切り抜き3chは再生の28%（89,707 / 317,531再生）を占めながら登録獲得は10人で、ゆっくり系との登録効率差は依然として大きい。平均タイトル実効長も 16.9〜19.5字で全ch最短。ただし切り抜きのタイトルは発言の引用なので、文字数下限を課すと誤引用を作るリスクがある。本日は適用を見送り、別施策（引用は保ったまま文脈を添える形）として扱う。</t>
         </is>
       </c>
     </row>
@@ -1400,14 +1400,22 @@
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
+          <t>④' 実効文字数の初版集計には実装バグがあり、同日中に検出して直した。旧実装の正規表現 `[#＃]\S+` が「一口SCP #110：SCP-███「投稿者の編集室」…」のような連番つきタイトルで本文を丸ごとハッシュタグと見なして落としており、実効41字を5字と数えていた（scp-lab 50本中14本が該当）。コロンで止める実装に修正し、レポートとbackend のゲートで同じ関数を使うようにした（別実装を持つとレポートの数字と実際に弾かれる基準がずれる）。結論（25〜29字が頂点の逆U字・下限20字）は修正後も変わらない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
           <t>⑤ 「なぜ〇〇なのか」疑問形は ch を選ぶ。scp-lab 1.32 vs 0.51（2.6倍・leave-one-out 後も 1.15）、daily-science 0.53 vs 0.18（3.0倍）、yokai-watch 0.61 vs 0.33、2ch-matome 0.25 vs 0.18 で有効。一方 pokemon-lab は 0.08 vs 0.41 で明確に逆効果、company-facts は疑問形が n=1 しかなく判断不能。09-11 朝の run はこの ch 差を正しく分けて適用できていた（09-10 の scp-lab「疑問形は負」判定が誤り）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A27:N27"/>
     <mergeCell ref="A26:N26"/>
+    <mergeCell ref="A30:N30"/>
     <mergeCell ref="A29:N29"/>
     <mergeCell ref="A25:N25"/>
     <mergeCell ref="A2:J2"/>
@@ -1615,11 +1623,11 @@
         <v>11306</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>21.7</v>
+        <v>30.3</v>
       </c>
       <c r="R2" s="8">
-        <f>IF(D2=0,"",13/D2)</f>
-        <v>0.26</v>
+        <f>IF(D2=0,"",3/D2)</f>
+        <v>0.06</v>
       </c>
       <c r="S2" s="4" t="n">
         <v>1.324</v>
@@ -1846,11 +1854,11 @@
         <v>9505</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>20.3</v>
+        <v>30.6</v>
       </c>
       <c r="R5" s="8">
-        <f>IF(D5=0,"",23/D5)</f>
-        <v>0.46</v>
+        <f>IF(D5=0,"",9/D5)</f>
+        <v>0.18</v>
       </c>
       <c r="S5" s="4" t="n">
         <v>0.534</v>
@@ -1923,11 +1931,11 @@
         <v>7648</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>23.4</v>
+        <v>30.2</v>
       </c>
       <c r="R6" s="8">
-        <f>IF(D6=0,"",13/D6)</f>
-        <v>0.265306</v>
+        <f>IF(D6=0,"",4/D6)</f>
+        <v>0.081633</v>
       </c>
       <c r="S6" s="4" t="n">
         <v>0.607</v>
@@ -2000,11 +2008,11 @@
         <v>6926</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>23.2</v>
+        <v>32</v>
       </c>
       <c r="R7" s="8">
-        <f>IF(D7=0,"",18/D7)</f>
-        <v>0.367347</v>
+        <f>IF(D7=0,"",5/D7)</f>
+        <v>0.102041</v>
       </c>
       <c r="S7" s="4" t="n">
         <v>0.076</v>
@@ -2391,7 +2399,7 @@
         <v>2860</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="R12" s="8">
         <f>IF(D12=0,"",7/D12)</f>
@@ -8073,11 +8081,11 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>架空論文ファイル  — 2,184人の記録</t>
+          <t>架空論文ファイル ：あなたの操作は脳波で読まれる — 2,184人の記録</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
@@ -8266,7 +8274,7 @@
       </c>
       <c r="E4" s="22" t="inlineStr">
         <is>
-          <t>n=330（views&gt;0）で登録/千再生は 0-14字 0.242 / 15-19字 0.279 / 20-24字 0.400 / 25-29字 0.637 / 30字以上 0.355。25〜29字が頂点の逆U字で、最弱帯の2.6倍。20字未満が全体の34%（112/330本）を占めていた。自然文の min_effective_chars_target は backend が読まないため1本も効いていなかった。</t>
+          <t>n=330（views&gt;0）で登録/千再生は 0-14字 0.104 / 15-19字 0.279 / 20-24字 0.402 / 25-29字 0.646 / 30-34字 0.389 / 35字以上 0.345。25〜29字が頂点の逆U字で、最弱帯の6.2倍。4分位でも同じ形（Q1 0.227 / Q2 0.476 / Q3 0.518 / Q4 0.352）。20字未満が全体の20%（66/330本）を占めていた。自然文の min_effective_chars_target は backend が読まないため1本も効いていなかった。</t>
         </is>
       </c>
       <c r="F4" s="22" t="inlineStr">
@@ -8441,7 +8449,7 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>切り抜き3chは 89,707再生（全体の46%）で登録10人。平均タイトル実効長は clip-fukada 16.1字 / clip-lab 18.2字 / clip-kaneko 19.3字 で全ch最短3つ、20字未満率は 88% / 62% / 54%。実効長と登録転換の関係（提案3）はここで最も伸びしろがある。ただしタイトルが発言の引用なので、文字数下限を機械的に課すと誤引用を作りうる。</t>
+          <t>切り抜き3chは 89,707再生（全体の28%）で登録10人。平均タイトル実効長は clip-fukada 16.9字 / clip-lab 18.2字 / clip-kaneko 19.5字 で全ch最短3つ、20字未満率は 85% / 67% / 53%。実効長と登録転換の関係（提案3）はここで最も伸びしろがある。ただしタイトルが発言の引用なので、文字数下限を機械的に課すと誤引用を作りうる。</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
